--- a/template_file/StockInExportTemplate.xlsx
+++ b/template_file/StockInExportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-andum\Toho-Project\cmwi\backend\template_file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-andum\cmwi\backend-cmw\template_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4278F557-D1DB-4AFA-BBC2-786829C0A6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6B0C77-1A8B-4310-80B7-1AF37D00FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4905" windowWidth="29040" windowHeight="15990" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Stock In</t>
   </si>
@@ -33,12 +33,6 @@
     <t xml:space="preserve"> Department : 75 - EQUIPMENT ASSURANCE</t>
   </si>
   <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Dept.</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -55,6 +49,15 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Rack</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Specification</t>
   </si>
 </sst>
 </file>
@@ -173,15 +176,6 @@
         <color theme="1"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="1"/>
       </top>
@@ -195,6 +189,21 @@
         <color theme="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -202,7 +211,7 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -210,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -224,22 +233,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,26 +619,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDEBEC8B-A9F7-4385-B560-5A66596CB4CB}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
     <col min="3" max="3" width="29.85546875" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="5" max="5" width="48.140625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="3"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -637,7 +648,7 @@
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
@@ -647,8 +658,8 @@
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -659,14 +670,14 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -677,14 +688,14 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -695,223 +706,40 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
